--- a/data/results/stat_graz/p_correct.xlsx
+++ b/data/results/stat_graz/p_correct.xlsx
@@ -708,7 +708,7 @@
         <v>100</v>
       </c>
       <c r="H2" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="I2" t="n">
         <v>100</v>
@@ -717,7 +717,7 @@
         <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="L2" t="n">
         <v>95</v>
@@ -726,13 +726,13 @@
         <v>85</v>
       </c>
       <c r="N2" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="O2" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="P2" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="Q2" t="n">
         <v>80</v>
@@ -750,7 +750,7 @@
         <v>90</v>
       </c>
       <c r="V2" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="W2" t="n">
         <v>90</v>
@@ -765,28 +765,28 @@
         <v>95</v>
       </c>
       <c r="AA2" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AB2" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AC2" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AD2" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="AE2" t="n">
         <v>100</v>
       </c>
       <c r="AF2" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AG2" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH2" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AI2" t="n">
         <v>95</v>
@@ -801,19 +801,19 @@
         <v>100</v>
       </c>
       <c r="AM2" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AN2" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AO2" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AP2" t="n">
         <v>85</v>
       </c>
       <c r="AQ2" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AR2" t="n">
         <v>70</v>
@@ -822,19 +822,19 @@
         <v>72.22</v>
       </c>
       <c r="AT2" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AU2" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AV2" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AW2" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AX2" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AY2" t="n">
         <v>85</v>
@@ -848,10 +848,10 @@
         <v>95</v>
       </c>
       <c r="C3" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D3" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E3" t="n">
         <v>100</v>
@@ -863,25 +863,25 @@
         <v>95</v>
       </c>
       <c r="H3" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="I3" t="n">
         <v>85</v>
       </c>
       <c r="J3" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="K3" t="n">
         <v>45</v>
       </c>
       <c r="L3" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="M3" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="N3" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="O3" t="n">
         <v>100</v>
@@ -899,7 +899,7 @@
         <v>95</v>
       </c>
       <c r="T3" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="U3" t="n">
         <v>95</v>
@@ -911,16 +911,16 @@
         <v>100</v>
       </c>
       <c r="X3" t="n">
+        <v>95</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>95</v>
+      </c>
+      <c r="AA3" t="n">
         <v>85</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>80</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>95</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>80</v>
       </c>
       <c r="AB3" t="n">
         <v>65</v>
@@ -932,13 +932,13 @@
         <v>90</v>
       </c>
       <c r="AE3" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AF3" t="n">
         <v>95</v>
       </c>
       <c r="AG3" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AH3" t="n">
         <v>100</v>
@@ -953,10 +953,10 @@
         <v>95</v>
       </c>
       <c r="AL3" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AM3" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AN3" t="n">
         <v>100</v>
@@ -968,31 +968,31 @@
         <v>90</v>
       </c>
       <c r="AQ3" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AR3" t="n">
         <v>100</v>
       </c>
       <c r="AS3" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AT3" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AU3" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="AV3" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AW3" t="n">
         <v>100</v>
       </c>
       <c r="AX3" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AY3" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
